--- a/AAII_Financials/Quarterly/PPLFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPLFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>PPLFY</t>
   </si>
@@ -656,80 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,8 +776,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +823,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +983,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,8 +1095,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1113,8 +1140,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1157,8 +1187,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,8 +1208,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1219,8 +1253,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,8 +1300,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,8 +1347,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1351,8 +1394,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,8 +1488,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1483,8 +1535,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1527,8 +1582,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1770,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1747,8 +1817,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1791,8 +1864,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,8 +1911,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1879,57 +1958,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2050,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E41" s="3">
         <v>461900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>454800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>413500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>401000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>385200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>338800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>60400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>301300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>300100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>292700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>262300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>277200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>272700</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,316 +2142,340 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E43" s="3">
         <v>14500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>42500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>285700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>17500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E44" s="3">
         <v>48100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>51500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>49200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>50600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>34100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>57500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>32300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>27400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>28000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>42400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>40200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14600</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>531100</v>
+      </c>
+      <c r="E46" s="3">
         <v>531000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>520800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>480400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>484200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>454500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>442100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>402600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>369900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>362200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>348800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>334100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>346200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>345800</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E47" s="3">
         <v>74300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>75400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>75700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>77900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>76300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>78600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>83200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>77100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>79500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>81700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>81500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>84000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>284700</v>
+      </c>
+      <c r="E48" s="3">
         <v>301100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>307200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>302900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>310800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>305100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>313900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>353700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>333400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>345000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>356900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>365700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>378000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>379900</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E49" s="3">
         <v>16100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2565,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2457,34 +2577,34 @@
         <v>900</v>
       </c>
       <c r="E52" s="3">
+        <v>900</v>
+      </c>
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>800</v>
       </c>
       <c r="H52" s="3">
         <v>800</v>
       </c>
       <c r="I52" s="3">
+        <v>800</v>
+      </c>
+      <c r="J52" s="3">
         <v>700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>2700</v>
       </c>
       <c r="O52" s="3">
         <v>2700</v>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>910900</v>
+      </c>
+      <c r="E54" s="3">
         <v>932700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>930300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>885800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>899300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>860800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>859900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>865500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>804800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>811100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>811900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>806500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>833700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>835400</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,52 +2746,56 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E57" s="3">
         <v>15900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2672,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>100</v>
@@ -2681,10 +2815,10 @@
         <v>100</v>
       </c>
       <c r="I58" s="3">
+        <v>100</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>300</v>
@@ -2699,101 +2833,110 @@
         <v>300</v>
       </c>
       <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E59" s="3">
         <v>17000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>25400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>30800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E60" s="3">
         <v>47100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>49600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>43600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>42100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>40200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>67000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>44900</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2819,25 +2962,28 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>100</v>
       </c>
       <c r="M61" s="3">
+        <v>100</v>
+      </c>
+      <c r="N61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E66" s="3">
         <v>83900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>85400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>109200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>78900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>79800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>80600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>90500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>93800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>118600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>97000</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>704300</v>
+      </c>
+      <c r="E72" s="3">
         <v>747400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>734900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>697200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>684100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>677900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>673000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>671100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>609000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>624100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>624400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>601300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>600300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>623100</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>800600</v>
+      </c>
+      <c r="E76" s="3">
         <v>849100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>838100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>800500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>790300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>782100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>780200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>785000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>714500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>732800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>736300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>712800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>715200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,57 +3703,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3607,8 +3802,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3634,43 +3833,46 @@
         <v>5900</v>
       </c>
       <c r="E83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F83" s="3">
         <v>24100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-12500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-12100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6000</v>
       </c>
       <c r="O83" s="3">
         <v>6000</v>
       </c>
       <c r="P83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6200</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E89" s="3">
         <v>17200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>51700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>55100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>60100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4171,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,52 +4378,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>26600</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>17600</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>23400</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,34 +4564,37 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
         <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
         <v>-26700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-17600</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
@@ -4357,100 +4603,109 @@
         <v>-100</v>
       </c>
       <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
         <v>-23500</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-100</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E102" s="3">
         <v>13700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>41700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>23500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15500</v>
       </c>
     </row>
